--- a/data/breathpubs_corr.xlsx
+++ b/data/breathpubs_corr.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10808"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/remy/Google Drive/projects/breathtmr/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\remra\COWORK\Publish BCT meta-analysis\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2AD27A0-21C1-1A47-9BBD-167CB71FA54E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFA2CD63-5F7A-4517-A7E8-E52BB555BC0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="460" windowWidth="13500" windowHeight="16720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="experiments" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="142">
   <si>
     <t>journal</t>
   </si>
@@ -474,6 +474,12 @@
   </si>
   <si>
     <t>MINDSENS</t>
+  </si>
+  <si>
+    <t>1a</t>
+  </si>
+  <si>
+    <t>1b</t>
   </si>
 </sst>
 </file>
@@ -1090,9 +1096,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1130,7 +1136,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1236,7 +1242,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1378,7 +1384,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1387,20 +1393,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q78"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.8125" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="4" width="10.83203125" style="4"/>
-    <col min="5" max="5" width="5.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.83203125" style="4"/>
-    <col min="7" max="7" width="16.33203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="4" width="10.8125" style="4"/>
+    <col min="5" max="5" width="5.6875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.8125" style="4"/>
+    <col min="7" max="7" width="16.3125" style="4" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15.5" style="4" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15.5" style="4" customWidth="1"/>
-    <col min="10" max="16" width="10.83203125" style="4"/>
+    <col min="10" max="16" width="10.8125" style="4"/>
     <col min="17" max="17" width="56.5" style="4" customWidth="1"/>
-    <col min="18" max="16384" width="10.83203125" style="4"/>
+    <col min="18" max="16384" width="10.8125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" s="1" customFormat="1" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1453,7 +1459,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -1503,7 +1509,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -1553,7 +1559,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -1603,7 +1609,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
@@ -1653,7 +1659,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
@@ -1703,7 +1709,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
@@ -1753,7 +1759,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
@@ -1803,7 +1809,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
@@ -1853,7 +1859,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
@@ -1903,7 +1909,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -1953,7 +1959,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A12" s="2" t="s">
         <v>10</v>
       </c>
@@ -1994,7 +2000,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A13" s="2" t="s">
         <v>10</v>
       </c>
@@ -2032,7 +2038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A14" s="2" t="s">
         <v>10</v>
       </c>
@@ -2070,7 +2076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A15" s="2" t="s">
         <v>10</v>
       </c>
@@ -2108,7 +2114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A16" s="2" t="s">
         <v>10</v>
       </c>
@@ -2146,7 +2152,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A17" s="2" t="s">
         <v>10</v>
       </c>
@@ -2184,7 +2190,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A18" s="2" t="s">
         <v>10</v>
       </c>
@@ -2222,7 +2228,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A19" s="2" t="s">
         <v>10</v>
       </c>
@@ -2260,7 +2266,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A20" s="2" t="s">
         <v>10</v>
       </c>
@@ -2298,7 +2304,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A21" s="2" t="s">
         <v>10</v>
       </c>
@@ -2336,7 +2342,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A22" s="2" t="s">
         <v>4</v>
       </c>
@@ -2386,7 +2392,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="23" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A23" s="2" t="s">
         <v>10</v>
       </c>
@@ -2436,7 +2442,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A24" s="2" t="s">
         <v>4</v>
       </c>
@@ -2483,7 +2489,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A25" s="2" t="s">
         <v>4</v>
       </c>
@@ -2530,7 +2536,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A26" s="2" t="s">
         <v>4</v>
       </c>
@@ -2580,7 +2586,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="27" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A27" s="2" t="s">
         <v>4</v>
       </c>
@@ -2627,7 +2633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A28" s="2" t="s">
         <v>4</v>
       </c>
@@ -2674,7 +2680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A29" s="2" t="s">
         <v>4</v>
       </c>
@@ -2721,7 +2727,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A30" s="2" t="s">
         <v>4</v>
       </c>
@@ -2768,7 +2774,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A31" s="3" t="s">
         <v>33</v>
       </c>
@@ -2785,7 +2791,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A32" s="3" t="s">
         <v>45</v>
       </c>
@@ -2805,7 +2811,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="33" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A33" s="3" t="s">
         <v>22</v>
       </c>
@@ -2825,7 +2831,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="34" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A34" s="2" t="s">
         <v>31</v>
       </c>
@@ -2838,8 +2844,8 @@
       <c r="D34" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="E34" s="2">
-        <v>1</v>
+      <c r="E34" s="2" t="s">
+        <v>141</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>8</v>
@@ -2869,7 +2875,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A35" s="2" t="s">
         <v>31</v>
       </c>
@@ -2882,8 +2888,8 @@
       <c r="D35" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="E35" s="2">
-        <v>1</v>
+      <c r="E35" s="2" t="s">
+        <v>141</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>8</v>
@@ -2913,7 +2919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A36" s="2" t="s">
         <v>31</v>
       </c>
@@ -2926,8 +2932,8 @@
       <c r="D36" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="E36" s="2">
-        <v>1</v>
+      <c r="E36" s="2" t="s">
+        <v>141</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>8</v>
@@ -2957,7 +2963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A37" s="2" t="s">
         <v>31</v>
       </c>
@@ -2970,8 +2976,8 @@
       <c r="D37" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="E37" s="2">
-        <v>1</v>
+      <c r="E37" s="2" t="s">
+        <v>141</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>8</v>
@@ -3001,7 +3007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A38" s="2" t="s">
         <v>31</v>
       </c>
@@ -3014,8 +3020,8 @@
       <c r="D38" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="E38" s="2">
-        <v>1</v>
+      <c r="E38" s="2" t="s">
+        <v>141</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>8</v>
@@ -3045,7 +3051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A39" s="2" t="s">
         <v>31</v>
       </c>
@@ -3058,8 +3064,8 @@
       <c r="D39" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="E39" s="2">
-        <v>1</v>
+      <c r="E39" s="2" t="s">
+        <v>141</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>8</v>
@@ -3089,7 +3095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A40" s="2" t="s">
         <v>31</v>
       </c>
@@ -3102,8 +3108,8 @@
       <c r="D40" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="E40" s="2">
-        <v>1</v>
+      <c r="E40" s="2" t="s">
+        <v>141</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>8</v>
@@ -3133,7 +3139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A41" s="2" t="s">
         <v>31</v>
       </c>
@@ -3146,8 +3152,8 @@
       <c r="D41" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="E41" s="2">
-        <v>1</v>
+      <c r="E41" s="2" t="s">
+        <v>141</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>8</v>
@@ -3177,7 +3183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A42" s="2" t="s">
         <v>31</v>
       </c>
@@ -3190,8 +3196,8 @@
       <c r="D42" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="E42" s="2">
-        <v>1</v>
+      <c r="E42" s="2" t="s">
+        <v>140</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>8</v>
@@ -3224,7 +3230,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="43" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A43" s="2" t="s">
         <v>31</v>
       </c>
@@ -3237,8 +3243,8 @@
       <c r="D43" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="E43" s="2">
-        <v>1</v>
+      <c r="E43" s="2" t="s">
+        <v>141</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>8</v>
@@ -3268,7 +3274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:17" s="2" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:17" s="2" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A44" s="2" t="s">
         <v>31</v>
       </c>
@@ -3281,8 +3287,8 @@
       <c r="D44" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="E44" s="2">
-        <v>1</v>
+      <c r="E44" s="2" t="s">
+        <v>140</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>8</v>
@@ -3312,7 +3318,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:17" s="2" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:17" s="2" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A45" s="2" t="s">
         <v>31</v>
       </c>
@@ -3325,8 +3331,8 @@
       <c r="D45" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="E45" s="2">
-        <v>1</v>
+      <c r="E45" s="2" t="s">
+        <v>141</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>8</v>
@@ -3356,7 +3362,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A46" s="2" t="s">
         <v>31</v>
       </c>
@@ -3369,8 +3375,8 @@
       <c r="D46" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="E46" s="2">
-        <v>1</v>
+      <c r="E46" s="2" t="s">
+        <v>141</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>8</v>
@@ -3400,7 +3406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A47" s="2" t="s">
         <v>31</v>
       </c>
@@ -3444,7 +3450,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A48" s="2" t="s">
         <v>31</v>
       </c>
@@ -3488,7 +3494,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A49" s="2" t="s">
         <v>31</v>
       </c>
@@ -3532,7 +3538,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A50" s="2" t="s">
         <v>31</v>
       </c>
@@ -3564,7 +3570,7 @@
         <v>137</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>4</v>
+        <v>83</v>
       </c>
       <c r="M50" s="2" t="s">
         <v>103</v>
@@ -3576,7 +3582,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A51" s="2" t="s">
         <v>31</v>
       </c>
@@ -3620,7 +3626,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A52" s="2" t="s">
         <v>31</v>
       </c>
@@ -3667,7 +3673,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="53" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A53" s="2" t="s">
         <v>31</v>
       </c>
@@ -3711,7 +3717,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A54" s="2" t="s">
         <v>31</v>
       </c>
@@ -3755,7 +3761,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.5">
       <c r="B55" s="3">
         <v>2015</v>
       </c>
@@ -3766,7 +3772,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A56" s="3" t="s">
         <v>44</v>
       </c>
@@ -3786,7 +3792,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="57" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A57" s="3" t="s">
         <v>4</v>
       </c>
@@ -3803,7 +3809,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A58" s="3" t="s">
         <v>34</v>
       </c>
@@ -3820,7 +3826,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="59" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.5">
       <c r="B59" s="3">
         <v>2017</v>
       </c>
@@ -3831,7 +3837,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A60" s="3" t="s">
         <v>36</v>
       </c>
@@ -3851,7 +3857,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="61" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A61" s="2" t="s">
         <v>4</v>
       </c>
@@ -3895,7 +3901,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A62" s="2" t="s">
         <v>4</v>
       </c>
@@ -3939,7 +3945,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A63" s="2" t="s">
         <v>4</v>
       </c>
@@ -3986,7 +3992,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="64" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A64" s="2" t="s">
         <v>4</v>
       </c>
@@ -4030,7 +4036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A65" s="2" t="s">
         <v>4</v>
       </c>
@@ -4074,7 +4080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.5">
       <c r="B66" s="3">
         <v>2019</v>
       </c>
@@ -4085,7 +4091,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="67" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A67" s="3" t="s">
         <v>45</v>
       </c>
@@ -4099,7 +4105,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="68" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A68" s="3" t="s">
         <v>4</v>
       </c>
@@ -4116,7 +4122,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="69" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A69" s="3" t="s">
         <v>30</v>
       </c>
@@ -4133,7 +4139,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="70" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A70" s="2" t="s">
         <v>44</v>
       </c>
@@ -4180,7 +4186,7 @@
       <c r="P70" s="2"/>
       <c r="Q70" s="2"/>
     </row>
-    <row r="71" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A71" s="2" t="s">
         <v>44</v>
       </c>
@@ -4227,7 +4233,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="72" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A72" s="2" t="s">
         <v>44</v>
       </c>
@@ -4274,7 +4280,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="73" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A73" s="2" t="s">
         <v>44</v>
       </c>
@@ -4321,7 +4327,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="74" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A74" s="2" t="s">
         <v>4</v>
       </c>
@@ -4365,7 +4371,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="75" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A75" s="2" t="s">
         <v>4</v>
       </c>
@@ -4406,7 +4412,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A76" s="2" t="s">
         <v>4</v>
       </c>
@@ -4447,7 +4453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A77" s="2" t="s">
         <v>4</v>
       </c>
@@ -4488,7 +4494,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A78" s="3"/>
       <c r="B78" s="3">
         <v>2021</v>
